--- a/artfynd/A 4468-2026 artfynd.xlsx
+++ b/artfynd/A 4468-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ55"/>
+  <dimension ref="A1:AZ56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133139617</v>
+        <v>133525220</v>
       </c>
       <c r="B2" t="n">
-        <v>92716</v>
+        <v>89547</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>757</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Apelsinticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,14 +714,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Teletornet NÖ, Teletornet NÖ, Dlr</t>
+          <t>A 4468, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535027</v>
+        <v>534985</v>
       </c>
       <c r="R2" t="n">
-        <v>6721978</v>
+        <v>6722026</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,22 +748,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Under gammal murken låga i kontinuitetstallskog. Mycket dålig mottagning för Artportalen.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,16 +795,16 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133139617</t>
+          <t>https://artportalen.se/Sighting/133525220</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119120258</v>
+        <v>133139617</v>
       </c>
       <c r="B3" t="n">
-        <v>93197</v>
+        <v>92716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +812,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>757</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -830,68 +835,63 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Teletornet NÖ, Teletornet NÖ, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534858</v>
+        <v>535027</v>
       </c>
       <c r="R3" t="n">
-        <v>6722027</v>
+        <v>6721978</v>
       </c>
       <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
         <v>1</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Falun</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Falun</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2024-08-14</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2024-08-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Nio från i år och en från förra året. På Falu kommuns mark där de genomförde en naturvårdsbränning för 8-10 år sedan.</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
       </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
@@ -905,19 +905,19 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119120258</t>
+          <t>https://artportalen.se/Sighting/133139617</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119550635</v>
+        <v>119120258</v>
       </c>
       <c r="B4" t="n">
         <v>93197</v>
@@ -946,19 +946,22 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>535033</v>
+        <v>534858</v>
       </c>
       <c r="R4" t="n">
-        <v>6721962</v>
+        <v>6722027</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,22 +985,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Nio från i år och en från förra året. På Falu kommuns mark där de genomförde en naturvårdsbränning för 8-10 år sedan.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,6 +1014,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1017,19 +1026,19 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119550635</t>
+          <t>https://artportalen.se/Sighting/119120258</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119623105</v>
+        <v>119550635</v>
       </c>
       <c r="B5" t="n">
         <v>93197</v>
@@ -1057,34 +1066,20 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Jungfruberget, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>534870</v>
+        <v>535033</v>
       </c>
       <c r="R5" t="n">
-        <v>6722037</v>
+        <v>6721962</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1108,22 +1103,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,27 +1133,27 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119623105</t>
+          <t>https://artportalen.se/Sighting/119550635</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131934104</v>
+        <v>119623105</v>
       </c>
       <c r="B6" t="n">
-        <v>93271</v>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,23 +1178,34 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>535034</v>
+        <v>534870</v>
       </c>
       <c r="R6" t="n">
-        <v>6722021</v>
+        <v>6722037</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1223,22 +1229,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,34 +1253,33 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131934104</t>
+          <t>https://artportalen.se/Sighting/119623105</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131931750</v>
+        <v>131934104</v>
       </c>
       <c r="B7" t="n">
-        <v>91995</v>
+        <v>93271</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1282,41 +1287,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>jungfruberget, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>534974</v>
+        <v>535034</v>
       </c>
       <c r="R7" t="n">
-        <v>6721990</v>
+        <v>6722021</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1348,7 +1349,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1358,7 +1359,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,24 +1375,24 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131931750</t>
+          <t>https://artportalen.se/Sighting/131934104</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133142883</v>
+        <v>131931750</v>
       </c>
       <c r="B8" t="n">
         <v>91995</v>
@@ -1421,26 +1422,22 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Backen TT, Backen TT, Dlr</t>
+          <t>jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>534896</v>
+        <v>534974</v>
       </c>
       <c r="R8" t="n">
-        <v>6721928</v>
+        <v>6721990</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1467,29 +1464,29 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
@@ -1498,121 +1495,124 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133142883</t>
+          <t>https://artportalen.se/Sighting/131931750</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115733713</v>
+        <v>133142883</v>
       </c>
       <c r="B9" t="n">
-        <v>57950</v>
+        <v>91995</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Backen TT, Backen TT, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>534819</v>
+        <v>534896</v>
       </c>
       <c r="R9" t="n">
-        <v>6722009</v>
+        <v>6721928</v>
       </c>
       <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
         <v>1</v>
       </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Falun</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Falun</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2024-04-07</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:21</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2024-04-07</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>09:21</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Östra gränsen. Hack runt om.</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1630,13 +1630,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115733713</t>
+          <t>https://artportalen.se/Sighting/133142883</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>115734365</v>
+        <v>115733713</v>
       </c>
       <c r="B10" t="n">
         <v>57950</v>
@@ -1667,11 +1667,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1679,10 +1675,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>534810</v>
+        <v>534819</v>
       </c>
       <c r="R10" t="n">
-        <v>6722014</v>
+        <v>6722009</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1714,7 +1710,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1724,12 +1720,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>död klen tall stående tall.</t>
+          <t>Östra gränsen. Hack runt om.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1755,13 +1751,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115734365</t>
+          <t>https://artportalen.se/Sighting/115733713</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>115734466</v>
+        <v>115734365</v>
       </c>
       <c r="B11" t="n">
         <v>57950</v>
@@ -1804,7 +1800,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>534801</v>
+        <v>534810</v>
       </c>
       <c r="R11" t="n">
         <v>6722014</v>
@@ -1839,7 +1835,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1849,19 +1845,19 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Klen tall med brott ovan jord, den lutar mot en klen gran.</t>
+          <t>död klen tall stående tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="b">
         <v>0</v>
@@ -1880,13 +1876,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115734466</t>
+          <t>https://artportalen.se/Sighting/115734365</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>115734662</v>
+        <v>115734466</v>
       </c>
       <c r="B12" t="n">
         <v>57950</v>
@@ -1929,10 +1925,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>534794</v>
+        <v>534801</v>
       </c>
       <c r="R12" t="n">
-        <v>6722008</v>
+        <v>6722014</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1964,7 +1960,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1974,19 +1970,19 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Blött!</t>
+          <t>Klen tall med brott ovan jord, den lutar mot en klen gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG12" t="b">
         <v>0</v>
@@ -2005,13 +2001,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115734662</t>
+          <t>https://artportalen.se/Sighting/115734466</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115735183</v>
+        <v>115734662</v>
       </c>
       <c r="B13" t="n">
         <v>57950</v>
@@ -2054,10 +2050,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>534789</v>
+        <v>534794</v>
       </c>
       <c r="R13" t="n">
-        <v>6722026</v>
+        <v>6722008</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -2089,7 +2085,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2099,7 +2095,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Blött!</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2125,13 +2126,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115735183</t>
+          <t>https://artportalen.se/Sighting/115734662</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>115735661</v>
+        <v>115735183</v>
       </c>
       <c r="B14" t="n">
         <v>57950</v>
@@ -2164,7 +2165,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2174,10 +2175,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>534796</v>
+        <v>534789</v>
       </c>
       <c r="R14" t="n">
-        <v>6722027</v>
+        <v>6722026</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2209,7 +2210,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2219,7 +2220,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2245,13 +2246,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115735661</t>
+          <t>https://artportalen.se/Sighting/115735183</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>115735802</v>
+        <v>115735661</v>
       </c>
       <c r="B15" t="n">
         <v>57950</v>
@@ -2294,10 +2295,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>534782</v>
+        <v>534796</v>
       </c>
       <c r="R15" t="n">
-        <v>6722050</v>
+        <v>6722027</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2329,7 +2330,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2339,7 +2340,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2365,13 +2366,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115735802</t>
+          <t>https://artportalen.se/Sighting/115735661</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>116708002</v>
+        <v>115735802</v>
       </c>
       <c r="B16" t="n">
         <v>57950</v>
@@ -2402,18 +2403,22 @@
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Jungfruberget, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>534817</v>
+        <v>534782</v>
       </c>
       <c r="R16" t="n">
-        <v>6721998</v>
+        <v>6722050</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2440,27 +2445,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-07</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>04:38</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-07</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>04:38</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>4:38 Oerhört vackert med orrspel i norr och soluppgång i öst.</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2486,13 +2486,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116708002</t>
+          <t>https://artportalen.se/Sighting/115735802</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119119706</v>
+        <v>116708002</v>
       </c>
       <c r="B17" t="n">
         <v>57950</v>
@@ -2521,19 +2521,23 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>534840</v>
+        <v>534817</v>
       </c>
       <c r="R17" t="n">
-        <v>6722003</v>
+        <v>6721998</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2557,22 +2561,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>04:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>04:38</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>4:38 Oerhört vackert med orrspel i norr och soluppgång i öst.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2598,16 +2607,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119119706</t>
+          <t>https://artportalen.se/Sighting/116708002</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131857452</v>
+        <v>119119706</v>
       </c>
       <c r="B18" t="n">
-        <v>57972</v>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2633,27 +2642,19 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>534901</v>
+        <v>534840</v>
       </c>
       <c r="R18" t="n">
-        <v>6721978</v>
+        <v>6722003</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2677,27 +2678,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:31</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Hästmyror i en tall som Johannes fällde 2025.</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2723,13 +2719,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131857452</t>
+          <t>https://artportalen.se/Sighting/119119706</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131860492</v>
+        <v>131857452</v>
       </c>
       <c r="B19" t="n">
         <v>57972</v>
@@ -2772,10 +2768,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>535039</v>
+        <v>534901</v>
       </c>
       <c r="R19" t="n">
-        <v>6721992</v>
+        <v>6721978</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2807,7 +2803,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2817,12 +2813,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ståga, tall, med hästmyror som spillkråkan kalasat på! 'Det finns mycket död ved i olika stadier.</t>
+          <t>Hästmyror i en tall som Johannes fällde 2025.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2848,13 +2844,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131860492</t>
+          <t>https://artportalen.se/Sighting/131857452</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131861178</v>
+        <v>131860492</v>
       </c>
       <c r="B20" t="n">
         <v>57972</v>
@@ -2887,7 +2883,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2897,10 +2893,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>534975</v>
+        <v>535039</v>
       </c>
       <c r="R20" t="n">
-        <v>6722036</v>
+        <v>6721992</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2932,7 +2928,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2942,7 +2938,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ståga, tall, med hästmyror som spillkråkan kalasat på! 'Det finns mycket död ved i olika stadier.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2968,13 +2969,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131861178</t>
+          <t>https://artportalen.se/Sighting/131860492</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131932494</v>
+        <v>131861178</v>
       </c>
       <c r="B21" t="n">
         <v>57972</v>
@@ -3007,7 +3008,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3017,13 +3018,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>534986</v>
+        <v>534975</v>
       </c>
       <c r="R21" t="n">
-        <v>6722058</v>
+        <v>6722036</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3047,22 +3048,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3082,19 +3083,19 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131932494</t>
+          <t>https://artportalen.se/Sighting/131861178</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131932788</v>
+        <v>131932494</v>
       </c>
       <c r="B22" t="n">
         <v>57972</v>
@@ -3127,7 +3128,7 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3137,10 +3138,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>535003</v>
+        <v>534986</v>
       </c>
       <c r="R22" t="n">
-        <v>6722088</v>
+        <v>6722058</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3172,7 +3173,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3182,7 +3183,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3208,13 +3209,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131932788</t>
+          <t>https://artportalen.se/Sighting/131932494</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131933786</v>
+        <v>131932788</v>
       </c>
       <c r="B23" t="n">
         <v>57972</v>
@@ -3243,19 +3244,27 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>535060</v>
+        <v>535003</v>
       </c>
       <c r="R23" t="n">
-        <v>6722004</v>
+        <v>6722088</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3284,7 +3293,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3294,7 +3303,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3309,24 +3318,24 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131933786</t>
+          <t>https://artportalen.se/Sighting/131932788</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132670790</v>
+        <v>131933786</v>
       </c>
       <c r="B24" t="n">
         <v>57972</v>
@@ -3361,10 +3370,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>534906</v>
+        <v>535060</v>
       </c>
       <c r="R24" t="n">
-        <v>6721984</v>
+        <v>6722004</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3391,22 +3400,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>20:37</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>20:37</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3421,24 +3430,24 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132670790</t>
+          <t>https://artportalen.se/Sighting/131933786</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133140857</v>
+        <v>132670790</v>
       </c>
       <c r="B25" t="n">
         <v>57972</v>
@@ -3469,14 +3478,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Teletornet NÖ, Falun, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>535045</v>
+        <v>534906</v>
       </c>
       <c r="R25" t="n">
-        <v>6721981</v>
+        <v>6721984</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3503,22 +3512,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>20:37</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>20:37</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3544,13 +3553,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133140857</t>
+          <t>https://artportalen.se/Sighting/132670790</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133430533</v>
+        <v>133140857</v>
       </c>
       <c r="B26" t="n">
         <v>57972</v>
@@ -3579,24 +3588,16 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Teletornet NÖ, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>534834</v>
+        <v>535045</v>
       </c>
       <c r="R26" t="n">
-        <v>6722003</v>
+        <v>6721981</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3623,22 +3624,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3664,13 +3665,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133430533</t>
+          <t>https://artportalen.se/Sighting/133140857</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133701691</v>
+        <v>133430533</v>
       </c>
       <c r="B27" t="n">
         <v>57972</v>
@@ -3709,17 +3710,17 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Jungfruberget, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>534875</v>
+        <v>534834</v>
       </c>
       <c r="R27" t="n">
-        <v>6721945</v>
+        <v>6722003</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3743,22 +3744,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>19:54</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>19:54</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3784,16 +3785,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133701691</t>
+          <t>https://artportalen.se/Sighting/133430533</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133701658</v>
+        <v>133701691</v>
       </c>
       <c r="B28" t="n">
-        <v>57967</v>
+        <v>57972</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3801,27 +3802,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100110</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3829,13 +3834,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>534898</v>
+        <v>534875</v>
       </c>
       <c r="R28" t="n">
-        <v>6721903</v>
+        <v>6721945</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3859,22 +3864,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3900,16 +3905,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133701658</t>
+          <t>https://artportalen.se/Sighting/133701691</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>115734062</v>
+        <v>133701658</v>
       </c>
       <c r="B29" t="n">
-        <v>5179</v>
+        <v>57967</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3917,37 +3922,41 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100526</v>
+        <v>100110</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>534847</v>
+        <v>534898</v>
       </c>
       <c r="R29" t="n">
-        <v>6722012</v>
+        <v>6721903</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3971,22 +3980,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-04-07</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-04-07</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4012,16 +4021,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115734062</t>
+          <t>https://artportalen.se/Sighting/133701658</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131856731</v>
+        <v>115734062</v>
       </c>
       <c r="B30" t="n">
-        <v>5181</v>
+        <v>5179</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4047,24 +4056,19 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>534891</v>
+        <v>534847</v>
       </c>
       <c r="R30" t="n">
-        <v>6721970</v>
+        <v>6722012</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4088,22 +4092,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2024-04-07</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2024-04-07</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4112,7 +4116,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4130,16 +4133,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131856731</t>
+          <t>https://artportalen.se/Sighting/115734062</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132670982</v>
+        <v>131856731</v>
       </c>
       <c r="B31" t="n">
-        <v>57165</v>
+        <v>5181</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4147,37 +4150,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102613</v>
+        <v>100526</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Teletornet NÖ, Falun, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>534968</v>
+        <v>534891</v>
       </c>
       <c r="R31" t="n">
-        <v>6722066</v>
+        <v>6721970</v>
       </c>
       <c r="S31" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4201,27 +4209,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>20:48</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>20:48</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Orrspelet hörs tydligt när trafiken gör avbrott</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4230,6 +4233,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4247,16 +4251,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132670982</t>
+          <t>https://artportalen.se/Sighting/131856731</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131860402</v>
+        <v>132670982</v>
       </c>
       <c r="B32" t="n">
-        <v>58131</v>
+        <v>57165</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4264,16 +4268,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103023</v>
+        <v>102613</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4284,17 +4288,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Teletornet NÖ, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>535046</v>
+        <v>534968</v>
       </c>
       <c r="R32" t="n">
-        <v>6721986</v>
+        <v>6722066</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4318,22 +4322,27 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>20:48</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>20:48</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Orrspelet hörs tydligt när trafiken gör avbrott</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4359,13 +4368,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131860402</t>
+          <t>https://artportalen.se/Sighting/132670982</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131933329</v>
+        <v>131860402</v>
       </c>
       <c r="B33" t="n">
         <v>58131</v>
@@ -4394,24 +4403,16 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>535029</v>
+        <v>535046</v>
       </c>
       <c r="R33" t="n">
-        <v>6722040</v>
+        <v>6721986</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4438,22 +4439,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4473,39 +4474,39 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131933329</t>
+          <t>https://artportalen.se/Sighting/131860402</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131860837</v>
+        <v>131933329</v>
       </c>
       <c r="B34" t="n">
-        <v>58624</v>
+        <v>58131</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103042</v>
+        <v>103023</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4528,10 +4529,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>535021</v>
+        <v>535029</v>
       </c>
       <c r="R34" t="n">
-        <v>6721985</v>
+        <v>6722040</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4558,22 +4559,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4593,19 +4594,19 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131860837</t>
+          <t>https://artportalen.se/Sighting/131933329</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133701660</v>
+        <v>131860837</v>
       </c>
       <c r="B35" t="n">
         <v>58624</v>
@@ -4636,21 +4637,25 @@
       <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Jungfruberget, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>534898</v>
+        <v>535021</v>
       </c>
       <c r="R35" t="n">
-        <v>6721903</v>
+        <v>6721985</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4674,22 +4679,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4715,33 +4720,33 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133701660</t>
+          <t>https://artportalen.se/Sighting/131860837</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133701664</v>
+        <v>133701660</v>
       </c>
       <c r="B36" t="n">
-        <v>58658</v>
+        <v>58624</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103044</v>
+        <v>103042</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4831,16 +4836,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133701664</t>
+          <t>https://artportalen.se/Sighting/133701660</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>69624299</v>
+        <v>133701664</v>
       </c>
       <c r="B37" t="n">
-        <v>8455</v>
+        <v>58658</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4848,37 +4853,41 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>103044</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lugnet, Dlr</t>
+          <t>Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>534931</v>
+        <v>534898</v>
       </c>
       <c r="R37" t="n">
-        <v>6721932</v>
+        <v>6721903</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4902,12 +4911,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2017-04-24</t>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2017-04-24</t>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4922,24 +4941,24 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ville Pokela</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ville Pokela</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/69624299</t>
+          <t>https://artportalen.se/Sighting/133701664</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>69624301</v>
+        <v>69624299</v>
       </c>
       <c r="B38" t="n">
         <v>8455</v>
@@ -4974,10 +4993,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>535034</v>
+        <v>534931</v>
       </c>
       <c r="R38" t="n">
-        <v>6721983</v>
+        <v>6721932</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5035,13 +5054,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/69624301</t>
+          <t>https://artportalen.se/Sighting/69624299</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>69624302</v>
+        <v>69624301</v>
       </c>
       <c r="B39" t="n">
         <v>8455</v>
@@ -5076,10 +5095,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>534941</v>
+        <v>535034</v>
       </c>
       <c r="R39" t="n">
-        <v>6722046</v>
+        <v>6721983</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5137,16 +5156,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/69624302</t>
+          <t>https://artportalen.se/Sighting/69624301</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131855987</v>
+        <v>69624302</v>
       </c>
       <c r="B40" t="n">
-        <v>8460</v>
+        <v>8455</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5174,14 +5193,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Lugnet, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>534881</v>
+        <v>534941</v>
       </c>
       <c r="R40" t="n">
-        <v>6722022</v>
+        <v>6722046</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5208,27 +5227,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>15:50</t>
+          <t>2017-04-24</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Område som gjorts naturvårdsbränning i</t>
+          <t>2017-04-24</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5243,24 +5247,24 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Ville Pokela</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Ville Pokela</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131855987</t>
+          <t>https://artportalen.se/Sighting/69624302</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131856439</v>
+        <v>131855987</v>
       </c>
       <c r="B41" t="n">
         <v>8460</v>
@@ -5289,21 +5293,16 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>534895</v>
+        <v>534881</v>
       </c>
       <c r="R41" t="n">
-        <v>6721975</v>
+        <v>6722022</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5335,7 +5334,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5345,12 +5344,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Många tallågor och så gott som alla har spår av Mindre märgborre.</t>
+          <t>Område som gjorts naturvårdsbränning i</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5359,7 +5358,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5377,13 +5375,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131856439</t>
+          <t>https://artportalen.se/Sighting/131855987</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131856819</v>
+        <v>131856439</v>
       </c>
       <c r="B42" t="n">
         <v>8460</v>
@@ -5423,10 +5421,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>534891</v>
+        <v>534895</v>
       </c>
       <c r="R42" t="n">
-        <v>6721970</v>
+        <v>6721975</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5458,7 +5456,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5468,12 +5466,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>i tallåga.</t>
+          <t>Många tallågor och så gott som alla har spår av Mindre märgborre.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5500,13 +5498,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131856819</t>
+          <t>https://artportalen.se/Sighting/131856439</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131931659</v>
+        <v>131856819</v>
       </c>
       <c r="B43" t="n">
         <v>8460</v>
@@ -5535,19 +5533,24 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>534931</v>
+        <v>534891</v>
       </c>
       <c r="R43" t="n">
-        <v>6721980</v>
+        <v>6721970</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5571,27 +5574,27 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Kammossa vitmossor skvattram</t>
+          <t>i tallåga.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5600,6 +5603,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5617,13 +5621,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131931659</t>
+          <t>https://artportalen.se/Sighting/131856819</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131935328</v>
+        <v>131931659</v>
       </c>
       <c r="B44" t="n">
         <v>8460</v>
@@ -5652,24 +5656,19 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>534911</v>
+        <v>534931</v>
       </c>
       <c r="R44" t="n">
-        <v>6721960</v>
+        <v>6721980</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5698,7 +5697,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5708,7 +5707,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Kammossa vitmossor skvattram</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5717,7 +5721,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5729,19 +5732,19 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131935328</t>
+          <t>https://artportalen.se/Sighting/131931659</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133139883</v>
+        <v>131935328</v>
       </c>
       <c r="B45" t="n">
         <v>8460</v>
@@ -5770,16 +5773,21 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Teletornet NÖ, Teletornet NÖ, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>535041</v>
+        <v>534911</v>
       </c>
       <c r="R45" t="n">
-        <v>6721981</v>
+        <v>6721960</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5806,22 +5814,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5830,6 +5838,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5841,19 +5850,19 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133139883</t>
+          <t>https://artportalen.se/Sighting/131935328</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133526848</v>
+        <v>133139883</v>
       </c>
       <c r="B46" t="n">
         <v>8460</v>
@@ -5882,21 +5891,16 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>A 4468, Dlr</t>
+          <t>Teletornet NÖ, Teletornet NÖ, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>534896</v>
+        <v>535041</v>
       </c>
       <c r="R46" t="n">
-        <v>6721928</v>
+        <v>6721981</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5928,7 +5932,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5938,7 +5942,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5947,7 +5951,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5965,13 +5968,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133526848</t>
+          <t>https://artportalen.se/Sighting/133139883</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133701633</v>
+        <v>133526848</v>
       </c>
       <c r="B47" t="n">
         <v>8460</v>
@@ -6007,14 +6010,14 @@
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Jungfruberget, Dlr</t>
+          <t>A 4468, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>534890</v>
+        <v>534896</v>
       </c>
       <c r="R47" t="n">
-        <v>6722048</v>
+        <v>6721928</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6041,22 +6044,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6083,63 +6086,56 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133701633</t>
+          <t>https://artportalen.se/Sighting/133526848</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131854070</v>
+        <v>133701633</v>
       </c>
       <c r="B48" t="n">
-        <v>99195</v>
+        <v>8460</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>534834</v>
+        <v>534890</v>
       </c>
       <c r="R48" t="n">
-        <v>6721994</v>
+        <v>6722048</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6166,27 +6162,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Jag kan ange exakta koordinater.</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6213,13 +6204,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131854070</t>
+          <t>https://artportalen.se/Sighting/133701633</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131932040</v>
+        <v>131854070</v>
       </c>
       <c r="B49" t="n">
         <v>99195</v>
@@ -6249,19 +6240,27 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>534978</v>
+        <v>534834</v>
       </c>
       <c r="R49" t="n">
-        <v>6722023</v>
+        <v>6721994</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6288,22 +6287,27 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Jag kan ange exakta koordinater.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6312,30 +6316,31 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131932040</t>
+          <t>https://artportalen.se/Sighting/131854070</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131933678</v>
+        <v>131932040</v>
       </c>
       <c r="B50" t="n">
         <v>99195</v>
@@ -6365,27 +6370,19 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>535032</v>
+        <v>534978</v>
       </c>
       <c r="R50" t="n">
-        <v>6722043</v>
+        <v>6722023</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6417,7 +6414,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6427,7 +6424,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6436,31 +6433,30 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131933678</t>
+          <t>https://artportalen.se/Sighting/131932040</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131933889</v>
+        <v>131933678</v>
       </c>
       <c r="B51" t="n">
         <v>99195</v>
@@ -6490,7 +6486,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6507,10 +6503,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>535047</v>
+        <v>535032</v>
       </c>
       <c r="R51" t="n">
-        <v>6722041</v>
+        <v>6722043</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6542,7 +6538,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6552,7 +6548,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6573,19 +6569,19 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131933889</t>
+          <t>https://artportalen.se/Sighting/131933678</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131933893</v>
+        <v>131933889</v>
       </c>
       <c r="B52" t="n">
         <v>99195</v>
@@ -6615,19 +6611,27 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>535068</v>
+        <v>535047</v>
       </c>
       <c r="R52" t="n">
-        <v>6722008</v>
+        <v>6722041</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6678,30 +6682,31 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131933893</t>
+          <t>https://artportalen.se/Sighting/131933889</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131933947</v>
+        <v>131933893</v>
       </c>
       <c r="B53" t="n">
         <v>99195</v>
@@ -6731,7 +6736,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6740,10 +6745,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>535052</v>
+        <v>535068</v>
       </c>
       <c r="R53" t="n">
-        <v>6722014</v>
+        <v>6722008</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6775,7 +6780,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6785,7 +6790,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6811,13 +6816,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131933947</t>
+          <t>https://artportalen.se/Sighting/131933893</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131934032</v>
+        <v>131933947</v>
       </c>
       <c r="B54" t="n">
         <v>99195</v>
@@ -6847,7 +6852,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6856,10 +6861,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>535044</v>
+        <v>535052</v>
       </c>
       <c r="R54" t="n">
-        <v>6722017</v>
+        <v>6722014</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6891,7 +6896,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6901,7 +6906,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6927,13 +6932,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131934032</t>
+          <t>https://artportalen.se/Sighting/131933947</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131937568</v>
+        <v>131934032</v>
       </c>
       <c r="B55" t="n">
         <v>99195</v>
@@ -6963,27 +6968,19 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Teletornet NÖ, Falun, Dlr</t>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>535010</v>
+        <v>535044</v>
       </c>
       <c r="R55" t="n">
-        <v>6721978</v>
+        <v>6722017</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7015,7 +7012,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7025,7 +7022,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7034,23 +7031,147 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131934032</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>131937568</v>
+      </c>
+      <c r="B56" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Teletornet NÖ, Falun, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>535010</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6721978</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/131937568</t>
         </is>
@@ -7112,6 +7233,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
